--- a/public/templates/orders-import-template.xlsx
+++ b/public/templates/orders-import-template.xlsx
@@ -1,41 +1,116 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22130"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dvinskikh.sergey\Desktop\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{572BF8EF-DD0D-41B5-BD07-A55133EA293D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="Заказы" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="28">
+  <si>
+    <t>SKU</t>
+  </si>
+  <si>
+    <t>10001</t>
+  </si>
+  <si>
+    <t>Иванов И.И.</t>
+  </si>
+  <si>
+    <t>+7 900 000-00-01</t>
+  </si>
+  <si>
+    <t>Омск, ул. Ленина, 10</t>
+  </si>
+  <si>
+    <t>Оставить у ворот</t>
+  </si>
+  <si>
+    <t>ST-001</t>
+  </si>
+  <si>
+    <t>Стартер 24V</t>
+  </si>
+  <si>
+    <t>ORD-10001</t>
+  </si>
+  <si>
+    <t>BLT-005</t>
+  </si>
+  <si>
+    <t>Болт М10</t>
+  </si>
+  <si>
+    <t>10002</t>
+  </si>
+  <si>
+    <t>Петров П.П.</t>
+  </si>
+  <si>
+    <t>+7 900 000-00-02</t>
+  </si>
+  <si>
+    <t>Тюмень, ул. Мира, 5</t>
+  </si>
+  <si>
+    <t>Позвонить за час</t>
+  </si>
+  <si>
+    <t>BELT-20</t>
+  </si>
+  <si>
+    <t>Ремень 20мм</t>
+  </si>
+  <si>
+    <t>ORD-10002</t>
+  </si>
+  <si>
+    <t>ORD-10003</t>
+  </si>
+  <si>
+    <t>Номер заказа</t>
+  </si>
+  <si>
+    <t>Получатель</t>
+  </si>
+  <si>
+    <t>Телефон</t>
+  </si>
+  <si>
+    <t>Адрес</t>
+  </si>
+  <si>
+    <t>Комментарий</t>
+  </si>
+  <si>
+    <t>Наименование</t>
+  </si>
+  <si>
+    <t>Количество</t>
+  </si>
+  <si>
+    <t>Внешний id</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -52,7 +127,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -60,18 +135,76 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -396,128 +529,747 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:J50"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="13.125" customWidth="1"/>
+    <col min="2" max="2" width="13" customWidth="1"/>
+    <col min="3" max="3" width="15.75" customWidth="1"/>
+    <col min="4" max="4" width="20.75" customWidth="1"/>
+    <col min="5" max="5" width="16.5" customWidth="1"/>
+    <col min="7" max="7" width="13.625" customWidth="1"/>
+    <col min="8" max="8" width="11.25" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>номер заказа</v>
-      </c>
-      <c r="B1" t="str">
-        <v>получатель</v>
-      </c>
-      <c r="C1" t="str">
-        <v>телефон</v>
-      </c>
-      <c r="D1" t="str">
-        <v>адрес</v>
-      </c>
-      <c r="E1" t="str">
-        <v>комментарий</v>
-      </c>
-      <c r="F1" t="str">
-        <v>SKU</v>
-      </c>
-      <c r="G1" t="str">
-        <v>наименование</v>
-      </c>
-      <c r="H1" t="str">
-        <v>количество</v>
-      </c>
-      <c r="I1" t="str">
-        <v>внешний id</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>10001</v>
-      </c>
-      <c r="B2" t="str">
-        <v>Иванов И.И.</v>
-      </c>
-      <c r="C2" t="str">
-        <v>+7 900 000-00-01</v>
-      </c>
-      <c r="D2" t="str">
-        <v>Омск, ул. Ленина, 10</v>
-      </c>
-      <c r="E2" t="str">
-        <v>Оставить у ворот</v>
-      </c>
-      <c r="F2" t="str">
-        <v>ST-001</v>
-      </c>
-      <c r="G2" t="str">
-        <v>Стартер 24V</v>
-      </c>
-      <c r="H2">
+    <row r="1" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="3"/>
+    </row>
+    <row r="2" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="I2" t="str">
-        <v>ORD-10001</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>10001</v>
-      </c>
-      <c r="B3" t="str">
-        <v>Иванов И.И.</v>
-      </c>
-      <c r="C3" t="str">
-        <v>+7 900 000-00-01</v>
-      </c>
-      <c r="D3" t="str">
-        <v>Омск, ул. Ленина, 10</v>
-      </c>
-      <c r="E3" t="str">
-        <v>Оставить у ворот</v>
-      </c>
-      <c r="F3" t="str">
-        <v>BLT-005</v>
-      </c>
-      <c r="G3" t="str">
-        <v>Болт М10</v>
-      </c>
-      <c r="H3">
+      <c r="B2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I3" t="str">
-        <v>ORD-10001</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>10002</v>
-      </c>
-      <c r="B4" t="str">
-        <v>Петров П.П.</v>
-      </c>
-      <c r="C4" t="str">
-        <v>+7 900 000-00-02</v>
-      </c>
-      <c r="D4" t="str">
-        <v>Тюмень, ул. Мира, 5</v>
-      </c>
-      <c r="E4" t="str">
-        <v>Позвонить за час</v>
-      </c>
-      <c r="F4" t="str">
-        <v>BELT-20</v>
-      </c>
-      <c r="G4" t="str">
-        <v>Ремень 20мм</v>
-      </c>
-      <c r="H4">
+      <c r="G2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" s="1">
+        <v>1</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J2" s="3"/>
+    </row>
+    <row r="3" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="I4" t="str">
-        <v>ORD-10002</v>
-      </c>
+      <c r="C3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H3" s="1">
+        <v>6</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J3" s="3"/>
+    </row>
+    <row r="4" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H4" s="1">
+        <v>2</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="J4" s="3"/>
+    </row>
+    <row r="5" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="3"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" s="1"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="2"/>
+      <c r="J6" s="3"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="3"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="3"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="3"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="3"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="3"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="3"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" s="1"/>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="3"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="3"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" s="1"/>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="3"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" s="1"/>
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="3"/>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17" s="1"/>
+      <c r="B17" s="1"/>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="3"/>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18" s="1"/>
+      <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1"/>
+      <c r="G18" s="1"/>
+      <c r="H18" s="1"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="3"/>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" s="1"/>
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="3"/>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20" s="1"/>
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="3"/>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A21" s="1"/>
+      <c r="B21" s="1"/>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1"/>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1"/>
+      <c r="I21" s="2"/>
+      <c r="J21" s="3"/>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A22" s="1"/>
+      <c r="B22" s="1"/>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1"/>
+      <c r="F22" s="1"/>
+      <c r="G22" s="1"/>
+      <c r="H22" s="1"/>
+      <c r="I22" s="2"/>
+      <c r="J22" s="3"/>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A23" s="1"/>
+      <c r="B23" s="1"/>
+      <c r="C23" s="1"/>
+      <c r="D23" s="1"/>
+      <c r="E23" s="1"/>
+      <c r="F23" s="1"/>
+      <c r="G23" s="1"/>
+      <c r="H23" s="1"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="3"/>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A24" s="1"/>
+      <c r="B24" s="1"/>
+      <c r="C24" s="1"/>
+      <c r="D24" s="1"/>
+      <c r="E24" s="1"/>
+      <c r="F24" s="1"/>
+      <c r="G24" s="1"/>
+      <c r="H24" s="1"/>
+      <c r="I24" s="2"/>
+      <c r="J24" s="3"/>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A25" s="1"/>
+      <c r="B25" s="1"/>
+      <c r="C25" s="1"/>
+      <c r="D25" s="1"/>
+      <c r="E25" s="1"/>
+      <c r="F25" s="1"/>
+      <c r="G25" s="1"/>
+      <c r="H25" s="1"/>
+      <c r="I25" s="2"/>
+      <c r="J25" s="3"/>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A26" s="1"/>
+      <c r="B26" s="1"/>
+      <c r="C26" s="1"/>
+      <c r="D26" s="1"/>
+      <c r="E26" s="1"/>
+      <c r="F26" s="1"/>
+      <c r="G26" s="1"/>
+      <c r="H26" s="1"/>
+      <c r="I26" s="2"/>
+      <c r="J26" s="3"/>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A27" s="1"/>
+      <c r="B27" s="1"/>
+      <c r="C27" s="1"/>
+      <c r="D27" s="1"/>
+      <c r="E27" s="1"/>
+      <c r="F27" s="1"/>
+      <c r="G27" s="1"/>
+      <c r="H27" s="1"/>
+      <c r="I27" s="2"/>
+      <c r="J27" s="3"/>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A28" s="1"/>
+      <c r="B28" s="1"/>
+      <c r="C28" s="1"/>
+      <c r="D28" s="1"/>
+      <c r="E28" s="1"/>
+      <c r="F28" s="1"/>
+      <c r="G28" s="1"/>
+      <c r="H28" s="1"/>
+      <c r="I28" s="2"/>
+      <c r="J28" s="3"/>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A29" s="1"/>
+      <c r="B29" s="1"/>
+      <c r="C29" s="1"/>
+      <c r="D29" s="1"/>
+      <c r="E29" s="1"/>
+      <c r="F29" s="1"/>
+      <c r="G29" s="1"/>
+      <c r="H29" s="1"/>
+      <c r="I29" s="2"/>
+      <c r="J29" s="3"/>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A30" s="1"/>
+      <c r="B30" s="1"/>
+      <c r="C30" s="1"/>
+      <c r="D30" s="1"/>
+      <c r="E30" s="1"/>
+      <c r="F30" s="1"/>
+      <c r="G30" s="1"/>
+      <c r="H30" s="1"/>
+      <c r="I30" s="2"/>
+      <c r="J30" s="3"/>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A31" s="1"/>
+      <c r="B31" s="1"/>
+      <c r="C31" s="1"/>
+      <c r="D31" s="1"/>
+      <c r="E31" s="1"/>
+      <c r="F31" s="1"/>
+      <c r="G31" s="1"/>
+      <c r="H31" s="1"/>
+      <c r="I31" s="2"/>
+      <c r="J31" s="3"/>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A32" s="1"/>
+      <c r="B32" s="1"/>
+      <c r="C32" s="1"/>
+      <c r="D32" s="1"/>
+      <c r="E32" s="1"/>
+      <c r="F32" s="1"/>
+      <c r="G32" s="1"/>
+      <c r="H32" s="1"/>
+      <c r="I32" s="2"/>
+      <c r="J32" s="3"/>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A33" s="1"/>
+      <c r="B33" s="1"/>
+      <c r="C33" s="1"/>
+      <c r="D33" s="1"/>
+      <c r="E33" s="1"/>
+      <c r="F33" s="1"/>
+      <c r="G33" s="1"/>
+      <c r="H33" s="1"/>
+      <c r="I33" s="2"/>
+      <c r="J33" s="3"/>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A34" s="1"/>
+      <c r="B34" s="1"/>
+      <c r="C34" s="1"/>
+      <c r="D34" s="1"/>
+      <c r="E34" s="1"/>
+      <c r="F34" s="1"/>
+      <c r="G34" s="1"/>
+      <c r="H34" s="1"/>
+      <c r="I34" s="2"/>
+      <c r="J34" s="3"/>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A35" s="1"/>
+      <c r="B35" s="1"/>
+      <c r="C35" s="1"/>
+      <c r="D35" s="1"/>
+      <c r="E35" s="1"/>
+      <c r="F35" s="1"/>
+      <c r="G35" s="1"/>
+      <c r="H35" s="1"/>
+      <c r="I35" s="2"/>
+      <c r="J35" s="3"/>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A36" s="1"/>
+      <c r="B36" s="1"/>
+      <c r="C36" s="1"/>
+      <c r="D36" s="1"/>
+      <c r="E36" s="1"/>
+      <c r="F36" s="1"/>
+      <c r="G36" s="1"/>
+      <c r="H36" s="1"/>
+      <c r="I36" s="2"/>
+      <c r="J36" s="3"/>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A37" s="1"/>
+      <c r="B37" s="1"/>
+      <c r="C37" s="1"/>
+      <c r="D37" s="1"/>
+      <c r="E37" s="1"/>
+      <c r="F37" s="1"/>
+      <c r="G37" s="1"/>
+      <c r="H37" s="1"/>
+      <c r="I37" s="2"/>
+      <c r="J37" s="3"/>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A38" s="1"/>
+      <c r="B38" s="1"/>
+      <c r="C38" s="1"/>
+      <c r="D38" s="1"/>
+      <c r="E38" s="1"/>
+      <c r="F38" s="1"/>
+      <c r="G38" s="1"/>
+      <c r="H38" s="1"/>
+      <c r="I38" s="2"/>
+      <c r="J38" s="3"/>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A39" s="1"/>
+      <c r="B39" s="1"/>
+      <c r="C39" s="1"/>
+      <c r="D39" s="1"/>
+      <c r="E39" s="1"/>
+      <c r="F39" s="1"/>
+      <c r="G39" s="1"/>
+      <c r="H39" s="1"/>
+      <c r="I39" s="2"/>
+      <c r="J39" s="3"/>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A40" s="1"/>
+      <c r="B40" s="1"/>
+      <c r="C40" s="1"/>
+      <c r="D40" s="1"/>
+      <c r="E40" s="1"/>
+      <c r="F40" s="1"/>
+      <c r="G40" s="1"/>
+      <c r="H40" s="1"/>
+      <c r="I40" s="2"/>
+      <c r="J40" s="3"/>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A41" s="1"/>
+      <c r="B41" s="1"/>
+      <c r="C41" s="1"/>
+      <c r="D41" s="1"/>
+      <c r="E41" s="1"/>
+      <c r="F41" s="1"/>
+      <c r="G41" s="1"/>
+      <c r="H41" s="1"/>
+      <c r="I41" s="2"/>
+      <c r="J41" s="3"/>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A42" s="1"/>
+      <c r="B42" s="1"/>
+      <c r="C42" s="1"/>
+      <c r="D42" s="1"/>
+      <c r="E42" s="1"/>
+      <c r="F42" s="1"/>
+      <c r="G42" s="1"/>
+      <c r="H42" s="1"/>
+      <c r="I42" s="2"/>
+      <c r="J42" s="3"/>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A43" s="1"/>
+      <c r="B43" s="1"/>
+      <c r="C43" s="1"/>
+      <c r="D43" s="1"/>
+      <c r="E43" s="1"/>
+      <c r="F43" s="1"/>
+      <c r="G43" s="1"/>
+      <c r="H43" s="1"/>
+      <c r="I43" s="2"/>
+      <c r="J43" s="3"/>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A44" s="1"/>
+      <c r="B44" s="1"/>
+      <c r="C44" s="1"/>
+      <c r="D44" s="1"/>
+      <c r="E44" s="1"/>
+      <c r="F44" s="1"/>
+      <c r="G44" s="1"/>
+      <c r="H44" s="1"/>
+      <c r="I44" s="2"/>
+      <c r="J44" s="3"/>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A45" s="1"/>
+      <c r="B45" s="1"/>
+      <c r="C45" s="1"/>
+      <c r="D45" s="1"/>
+      <c r="E45" s="1"/>
+      <c r="F45" s="1"/>
+      <c r="G45" s="1"/>
+      <c r="H45" s="1"/>
+      <c r="I45" s="2"/>
+      <c r="J45" s="3"/>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A46" s="1"/>
+      <c r="B46" s="1"/>
+      <c r="C46" s="1"/>
+      <c r="D46" s="1"/>
+      <c r="E46" s="1"/>
+      <c r="F46" s="1"/>
+      <c r="G46" s="1"/>
+      <c r="H46" s="1"/>
+      <c r="I46" s="2"/>
+      <c r="J46" s="3"/>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A47" s="1"/>
+      <c r="B47" s="1"/>
+      <c r="C47" s="1"/>
+      <c r="D47" s="1"/>
+      <c r="E47" s="1"/>
+      <c r="F47" s="1"/>
+      <c r="G47" s="1"/>
+      <c r="H47" s="1"/>
+      <c r="I47" s="2"/>
+      <c r="J47" s="3"/>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A48" s="1"/>
+      <c r="B48" s="1"/>
+      <c r="C48" s="1"/>
+      <c r="D48" s="1"/>
+      <c r="E48" s="1"/>
+      <c r="F48" s="1"/>
+      <c r="G48" s="1"/>
+      <c r="H48" s="1"/>
+      <c r="I48" s="2"/>
+      <c r="J48" s="3"/>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A49" s="1"/>
+      <c r="B49" s="1"/>
+      <c r="C49" s="1"/>
+      <c r="D49" s="1"/>
+      <c r="E49" s="1"/>
+      <c r="F49" s="1"/>
+      <c r="G49" s="1"/>
+      <c r="H49" s="1"/>
+      <c r="I49" s="2"/>
+      <c r="J49" s="3"/>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A50" s="1"/>
+      <c r="B50" s="1"/>
+      <c r="C50" s="1"/>
+      <c r="D50" s="1"/>
+      <c r="E50" s="1"/>
+      <c r="F50" s="1"/>
+      <c r="G50" s="1"/>
+      <c r="H50" s="1"/>
+      <c r="I50" s="2"/>
+      <c r="J50" s="3"/>
     </row>
   </sheetData>
+  <mergeCells count="50">
+    <mergeCell ref="I48:J48"/>
+    <mergeCell ref="I49:J49"/>
+    <mergeCell ref="I50:J50"/>
+    <mergeCell ref="I42:J42"/>
+    <mergeCell ref="I43:J43"/>
+    <mergeCell ref="I44:J44"/>
+    <mergeCell ref="I45:J45"/>
+    <mergeCell ref="I46:J46"/>
+    <mergeCell ref="I47:J47"/>
+    <mergeCell ref="I36:J36"/>
+    <mergeCell ref="I37:J37"/>
+    <mergeCell ref="I38:J38"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="I30:J30"/>
+    <mergeCell ref="I31:J31"/>
+    <mergeCell ref="I32:J32"/>
+    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="I34:J34"/>
+    <mergeCell ref="I35:J35"/>
+    <mergeCell ref="I24:J24"/>
+    <mergeCell ref="I25:J25"/>
+    <mergeCell ref="I26:J26"/>
+    <mergeCell ref="I27:J27"/>
+    <mergeCell ref="I28:J28"/>
+    <mergeCell ref="I29:J29"/>
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="I19:J19"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="I22:J22"/>
+    <mergeCell ref="I23:J23"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="I5:J5"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I4"/>
+    <ignoredError sqref="F1 A4:H4 A2:G2 I2 A3:H3" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/public/templates/orders-import-template.xlsx
+++ b/public/templates/orders-import-template.xlsx
@@ -1,28 +1,46 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22130"/>
-  <workbookPr codeName="ThisWorkbook"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dvinskikh.sergey\Desktop\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{572BF8EF-DD0D-41B5-BD07-A55133EA293D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
   </bookViews>
   <sheets>
-    <sheet name="Заказы" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="Заказы" state="visible" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="28">
   <si>
-    <t>SKU</t>
+    <t>Номер заказа</t>
+  </si>
+  <si>
+    <t>Получатель</t>
+  </si>
+  <si>
+    <t>Телефон</t>
+  </si>
+  <si>
+    <t>Адрес</t>
+  </si>
+  <si>
+    <t>Комментарий</t>
+  </si>
+  <si>
+    <t>Артикул</t>
+  </si>
+  <si>
+    <t>Наименование</t>
+  </si>
+  <si>
+    <t>Количество</t>
+  </si>
+  <si>
+    <t>Внешний id</t>
   </si>
   <si>
     <t>10001</t>
@@ -55,6 +73,9 @@
     <t>Болт М10</t>
   </si>
   <si>
+    <t>ORD-10002</t>
+  </si>
+  <si>
     <t>10002</t>
   </si>
   <si>
@@ -76,47 +97,27 @@
     <t>Ремень 20мм</t>
   </si>
   <si>
-    <t>ORD-10002</t>
-  </si>
-  <si>
     <t>ORD-10003</t>
-  </si>
-  <si>
-    <t>Номер заказа</t>
-  </si>
-  <si>
-    <t>Получатель</t>
-  </si>
-  <si>
-    <t>Телефон</t>
-  </si>
-  <si>
-    <t>Адрес</t>
-  </si>
-  <si>
-    <t>Комментарий</t>
-  </si>
-  <si>
-    <t>Наименование</t>
-  </si>
-  <si>
-    <t>Количество</t>
-  </si>
-  <si>
-    <t>Внешний id</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
-      <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <color theme="1"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+      <sz val="12"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -181,22 +182,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -529,9 +530,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J50"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.125" customWidth="1"/>
     <col min="2" max="2" width="13" customWidth="1"/>
@@ -542,127 +543,127 @@
     <col min="8" max="8" width="11.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" ht="15.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="J1" s="3"/>
     </row>
-    <row r="2" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" ht="15.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="H2" s="1">
         <v>1</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="J2" s="3"/>
     </row>
-    <row r="3" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" ht="15.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="H3" s="1">
         <v>6</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J3" s="3"/>
     </row>
-    <row r="4" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" ht="15.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="H4" s="1">
         <v>2</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="J4" s="3"/>
     </row>
-    <row r="5" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" ht="15.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
@@ -1216,60 +1217,57 @@
     </row>
   </sheetData>
   <mergeCells count="50">
-    <mergeCell ref="I48:J48"/>
-    <mergeCell ref="I49:J49"/>
-    <mergeCell ref="I50:J50"/>
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="I19:J19"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="I22:J22"/>
+    <mergeCell ref="I23:J23"/>
+    <mergeCell ref="I24:J24"/>
+    <mergeCell ref="I25:J25"/>
+    <mergeCell ref="I26:J26"/>
+    <mergeCell ref="I27:J27"/>
+    <mergeCell ref="I28:J28"/>
+    <mergeCell ref="I29:J29"/>
+    <mergeCell ref="I30:J30"/>
+    <mergeCell ref="I31:J31"/>
+    <mergeCell ref="I32:J32"/>
+    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="I34:J34"/>
+    <mergeCell ref="I35:J35"/>
+    <mergeCell ref="I36:J36"/>
+    <mergeCell ref="I37:J37"/>
+    <mergeCell ref="I38:J38"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="I41:J41"/>
     <mergeCell ref="I42:J42"/>
     <mergeCell ref="I43:J43"/>
     <mergeCell ref="I44:J44"/>
     <mergeCell ref="I45:J45"/>
     <mergeCell ref="I46:J46"/>
     <mergeCell ref="I47:J47"/>
-    <mergeCell ref="I36:J36"/>
-    <mergeCell ref="I37:J37"/>
-    <mergeCell ref="I38:J38"/>
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="I30:J30"/>
-    <mergeCell ref="I31:J31"/>
-    <mergeCell ref="I32:J32"/>
-    <mergeCell ref="I33:J33"/>
-    <mergeCell ref="I34:J34"/>
-    <mergeCell ref="I35:J35"/>
-    <mergeCell ref="I24:J24"/>
-    <mergeCell ref="I25:J25"/>
-    <mergeCell ref="I26:J26"/>
-    <mergeCell ref="I27:J27"/>
-    <mergeCell ref="I28:J28"/>
-    <mergeCell ref="I29:J29"/>
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="I19:J19"/>
-    <mergeCell ref="I20:J20"/>
-    <mergeCell ref="I21:J21"/>
-    <mergeCell ref="I22:J22"/>
-    <mergeCell ref="I23:J23"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="I1:J1"/>
-    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="I48:J48"/>
+    <mergeCell ref="I49:J49"/>
+    <mergeCell ref="I50:J50"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <ignoredErrors>
-    <ignoredError sqref="F1 A4:H4 A2:G2 I2 A3:H3" numberStoredAsText="1"/>
-  </ignoredErrors>
 </worksheet>
 </file>